--- a/results/mnist_0.1_result.xlsx
+++ b/results/mnist_0.1_result.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20380"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20382"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="1" documentId="5_{7C740BE4-A18A-4B4A-95AA-A6390FD911DD}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{A04025B9-30AF-44C8-BA24-47729593C85A}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="5_{7C740BE4-A18A-4B4A-95AA-A6390FD911DD}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{44611A12-0B3A-4A07-B7ED-9E8EC6EF3A65}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -15,21 +15,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>image</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -52,14 +43,6 @@
   </si>
   <si>
     <t>BTime_NN</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>new_SR</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>new_NN</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -385,15 +368,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H101"/>
+  <dimension ref="A1:F101"/>
   <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="13.46484375" customWidth="1"/>
     <col min="5" max="5" width="11.73046875" customWidth="1"/>
-    <col min="7" max="7" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -412,14 +394,8 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>1</v>
       </c>
@@ -438,14 +414,8 @@
       <c r="F2">
         <v>0.31</v>
       </c>
-      <c r="G2">
-        <v>0.6</v>
-      </c>
-      <c r="H2">
-        <v>0.96</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>2</v>
       </c>
@@ -464,14 +434,8 @@
       <c r="F3">
         <v>0.31</v>
       </c>
-      <c r="G3">
-        <v>0.31</v>
-      </c>
-      <c r="H3">
-        <v>0.33</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>3</v>
       </c>
@@ -490,14 +454,8 @@
       <c r="F4">
         <v>0.31</v>
       </c>
-      <c r="G4">
-        <v>0.31</v>
-      </c>
-      <c r="H4">
-        <v>0.32</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>4</v>
       </c>
@@ -516,14 +474,8 @@
       <c r="F5">
         <v>0.31</v>
       </c>
-      <c r="G5">
-        <v>0.31</v>
-      </c>
-      <c r="H5">
-        <v>0.31</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>5</v>
       </c>
@@ -542,14 +494,8 @@
       <c r="F6">
         <v>0.31</v>
       </c>
-      <c r="G6">
-        <v>0.31</v>
-      </c>
-      <c r="H6">
-        <v>0.31</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>6</v>
       </c>
@@ -568,14 +514,8 @@
       <c r="F7">
         <v>0.31</v>
       </c>
-      <c r="G7">
-        <v>0.31</v>
-      </c>
-      <c r="H7">
-        <v>0.31</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A8">
         <v>7</v>
       </c>
@@ -594,14 +534,8 @@
       <c r="F8">
         <v>185.12</v>
       </c>
-      <c r="G8">
-        <v>302.10000000000002</v>
-      </c>
-      <c r="H8">
-        <v>304.58</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A9">
         <v>8</v>
       </c>
@@ -620,14 +554,8 @@
       <c r="F9">
         <v>7.95</v>
       </c>
-      <c r="G9">
-        <v>4.9800000000000004</v>
-      </c>
-      <c r="H9">
-        <v>8.85</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A10">
         <v>9</v>
       </c>
@@ -646,14 +574,8 @@
       <c r="F10">
         <v>29</v>
       </c>
-      <c r="G10">
-        <v>52.82</v>
-      </c>
-      <c r="H10">
-        <v>161.19999999999999</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A11">
         <v>10</v>
       </c>
@@ -672,14 +594,8 @@
       <c r="F11">
         <v>0.31</v>
       </c>
-      <c r="G11">
-        <v>0.35</v>
-      </c>
-      <c r="H11">
-        <v>0.36</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A12">
         <v>11</v>
       </c>
@@ -698,14 +614,8 @@
       <c r="F12">
         <v>0.31</v>
       </c>
-      <c r="G12">
-        <v>0.32</v>
-      </c>
-      <c r="H12">
-        <v>0.31</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A13">
         <v>12</v>
       </c>
@@ -724,14 +634,8 @@
       <c r="F13">
         <v>13.3</v>
       </c>
-      <c r="G13">
-        <v>4.04</v>
-      </c>
-      <c r="H13">
-        <v>14.5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A14">
         <v>13</v>
       </c>
@@ -750,14 +654,8 @@
       <c r="F14">
         <v>4.07</v>
       </c>
-      <c r="G14">
-        <v>3.11</v>
-      </c>
-      <c r="H14">
-        <v>4.9800000000000004</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A15">
         <v>14</v>
       </c>
@@ -776,14 +674,8 @@
       <c r="F15">
         <v>0.31</v>
       </c>
-      <c r="G15">
-        <v>0.37</v>
-      </c>
-      <c r="H15">
-        <v>0.37</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A16">
         <v>15</v>
       </c>
@@ -802,14 +694,8 @@
       <c r="F16">
         <v>0.31</v>
       </c>
-      <c r="G16">
-        <v>0.32</v>
-      </c>
-      <c r="H16">
-        <v>0.31</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A17">
         <v>16</v>
       </c>
@@ -828,14 +714,8 @@
       <c r="F17">
         <v>1.2</v>
       </c>
-      <c r="G17">
-        <v>1.21</v>
-      </c>
-      <c r="H17">
-        <v>1.21</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A18">
         <v>17</v>
       </c>
@@ -854,14 +734,8 @@
       <c r="F18">
         <v>0.31</v>
       </c>
-      <c r="G18">
-        <v>0.32</v>
-      </c>
-      <c r="H18">
-        <v>0.31</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A19">
         <v>18</v>
       </c>
@@ -880,14 +754,8 @@
       <c r="F19">
         <v>0.31</v>
       </c>
-      <c r="G19">
-        <v>0.32</v>
-      </c>
-      <c r="H19">
-        <v>0.31</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A20">
         <v>19</v>
       </c>
@@ -906,14 +774,8 @@
       <c r="F20">
         <v>303.32</v>
       </c>
-      <c r="G20">
-        <v>307.33</v>
-      </c>
-      <c r="H20">
-        <v>300.73</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A21">
         <v>20</v>
       </c>
@@ -932,14 +794,8 @@
       <c r="F21">
         <v>0.31</v>
       </c>
-      <c r="G21">
-        <v>0.32</v>
-      </c>
-      <c r="H21">
-        <v>0.32</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A22">
         <v>21</v>
       </c>
@@ -958,14 +814,8 @@
       <c r="F22">
         <v>0.31</v>
       </c>
-      <c r="G22">
-        <v>0.32</v>
-      </c>
-      <c r="H22">
-        <v>0.31</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A23">
         <v>22</v>
       </c>
@@ -984,14 +834,8 @@
       <c r="F23">
         <v>0.31</v>
       </c>
-      <c r="G23">
-        <v>0.32</v>
-      </c>
-      <c r="H23">
-        <v>0.31</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A24">
         <v>23</v>
       </c>
@@ -1010,14 +854,8 @@
       <c r="F24">
         <v>6.94</v>
       </c>
-      <c r="G24">
-        <v>5.07</v>
-      </c>
-      <c r="H24">
-        <v>8.76</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A25">
         <v>24</v>
       </c>
@@ -1036,14 +874,8 @@
       <c r="F25">
         <v>0.31</v>
       </c>
-      <c r="G25">
-        <v>0.37</v>
-      </c>
-      <c r="H25">
-        <v>0.35</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A26">
         <v>25</v>
       </c>
@@ -1062,14 +894,8 @@
       <c r="F26">
         <v>15.1</v>
       </c>
-      <c r="G26">
-        <v>5.07</v>
-      </c>
-      <c r="H26">
-        <v>7.76</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A27">
         <v>26</v>
       </c>
@@ -1088,14 +914,8 @@
       <c r="F27">
         <v>0.31</v>
       </c>
-      <c r="G27">
-        <v>0.36</v>
-      </c>
-      <c r="H27">
-        <v>0.37</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A28">
         <v>27</v>
       </c>
@@ -1114,14 +934,8 @@
       <c r="F28">
         <v>0.31</v>
       </c>
-      <c r="G28">
-        <v>0.32</v>
-      </c>
-      <c r="H28">
-        <v>0.31</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A29">
         <v>28</v>
       </c>
@@ -1140,14 +954,8 @@
       <c r="F29">
         <v>0.31</v>
       </c>
-      <c r="G29">
-        <v>0.32</v>
-      </c>
-      <c r="H29">
-        <v>0.31</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A30">
         <v>29</v>
       </c>
@@ -1166,14 +974,8 @@
       <c r="F30">
         <v>0.31</v>
       </c>
-      <c r="G30">
-        <v>0.32</v>
-      </c>
-      <c r="H30">
-        <v>0.31</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A31">
         <v>30</v>
       </c>
@@ -1192,14 +994,8 @@
       <c r="F31">
         <v>0.31</v>
       </c>
-      <c r="G31">
-        <v>0.32</v>
-      </c>
-      <c r="H31">
-        <v>0.31</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A32">
         <v>31</v>
       </c>
@@ -1218,14 +1014,8 @@
       <c r="F32">
         <v>0.31</v>
       </c>
-      <c r="G32">
-        <v>0.32</v>
-      </c>
-      <c r="H32">
-        <v>0.31</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A33">
         <v>32</v>
       </c>
@@ -1244,14 +1034,8 @@
       <c r="F33">
         <v>0.31</v>
       </c>
-      <c r="G33">
-        <v>0.32</v>
-      </c>
-      <c r="H33">
-        <v>0.31</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A34">
         <v>33</v>
       </c>
@@ -1270,14 +1054,8 @@
       <c r="F34">
         <v>0.31</v>
       </c>
-      <c r="G34">
-        <v>0.32</v>
-      </c>
-      <c r="H34">
-        <v>0.31</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A35">
         <v>34</v>
       </c>
@@ -1296,14 +1074,8 @@
       <c r="F35">
         <v>0.31</v>
       </c>
-      <c r="G35">
-        <v>0.32</v>
-      </c>
-      <c r="H35">
-        <v>0.32</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A36">
         <v>35</v>
       </c>
@@ -1322,14 +1094,8 @@
       <c r="F36">
         <v>0.31</v>
       </c>
-      <c r="G36">
-        <v>0.32</v>
-      </c>
-      <c r="H36">
-        <v>0.32</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A37">
         <v>36</v>
       </c>
@@ -1348,14 +1114,8 @@
       <c r="F37">
         <v>0.31</v>
       </c>
-      <c r="G37">
-        <v>0.32</v>
-      </c>
-      <c r="H37">
-        <v>0.32</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A38">
         <v>37</v>
       </c>
@@ -1374,14 +1134,8 @@
       <c r="F38">
         <v>0.31</v>
       </c>
-      <c r="G38">
-        <v>0.32</v>
-      </c>
-      <c r="H38">
-        <v>0.32</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A39">
         <v>38</v>
       </c>
@@ -1400,14 +1154,8 @@
       <c r="F39">
         <v>0.31</v>
       </c>
-      <c r="G39">
-        <v>0.32</v>
-      </c>
-      <c r="H39">
-        <v>0.32</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A40">
         <v>39</v>
       </c>
@@ -1426,14 +1174,8 @@
       <c r="F40">
         <v>2.15</v>
       </c>
-      <c r="G40">
-        <v>2.17</v>
-      </c>
-      <c r="H40">
-        <v>5.17</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A41">
         <v>40</v>
       </c>
@@ -1452,14 +1194,8 @@
       <c r="F41">
         <v>0.31</v>
       </c>
-      <c r="G41">
-        <v>0.35</v>
-      </c>
-      <c r="H41">
-        <v>0.35</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A42">
         <v>41</v>
       </c>
@@ -1478,14 +1214,8 @@
       <c r="F42">
         <v>0.31</v>
       </c>
-      <c r="G42">
-        <v>0.32</v>
-      </c>
-      <c r="H42">
-        <v>0.31</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A43">
         <v>42</v>
       </c>
@@ -1504,14 +1234,8 @@
       <c r="F43">
         <v>0.31</v>
       </c>
-      <c r="G43">
-        <v>0.32</v>
-      </c>
-      <c r="H43">
-        <v>0.31</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A44">
         <v>43</v>
       </c>
@@ -1530,14 +1254,8 @@
       <c r="F44">
         <v>0.31</v>
       </c>
-      <c r="G44">
-        <v>0.32</v>
-      </c>
-      <c r="H44">
-        <v>0.31</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A45">
         <v>44</v>
       </c>
@@ -1556,14 +1274,8 @@
       <c r="F45">
         <v>4.05</v>
       </c>
-      <c r="G45">
-        <v>5.07</v>
-      </c>
-      <c r="H45">
-        <v>5.03</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A46">
         <v>45</v>
       </c>
@@ -1582,14 +1294,8 @@
       <c r="F46">
         <v>0.31</v>
       </c>
-      <c r="G46">
-        <v>0.35</v>
-      </c>
-      <c r="H46">
-        <v>0.36</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A47">
         <v>46</v>
       </c>
@@ -1608,14 +1314,8 @@
       <c r="F47">
         <v>5.0599999999999996</v>
       </c>
-      <c r="G47">
-        <v>5.09</v>
-      </c>
-      <c r="H47">
-        <v>10.039999999999999</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A48">
         <v>47</v>
       </c>
@@ -1634,14 +1334,8 @@
       <c r="F48">
         <v>0.31</v>
       </c>
-      <c r="G48">
-        <v>0.34</v>
-      </c>
-      <c r="H48">
-        <v>0.37</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A49">
         <v>48</v>
       </c>
@@ -1660,14 +1354,8 @@
       <c r="F49">
         <v>5.0999999999999996</v>
       </c>
-      <c r="G49">
-        <v>4.08</v>
-      </c>
-      <c r="H49">
-        <v>5.93</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A50">
         <v>49</v>
       </c>
@@ -1686,14 +1374,8 @@
       <c r="F50">
         <v>0.31</v>
       </c>
-      <c r="G50">
-        <v>0.37</v>
-      </c>
-      <c r="H50">
-        <v>0.34</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A51">
         <v>50</v>
       </c>
@@ -1712,14 +1394,8 @@
       <c r="F51">
         <v>0.31</v>
       </c>
-      <c r="G51">
-        <v>0.32</v>
-      </c>
-      <c r="H51">
-        <v>0.31</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A52">
         <v>51</v>
       </c>
@@ -1738,14 +1414,8 @@
       <c r="F52">
         <v>0.31</v>
       </c>
-      <c r="G52">
-        <v>0.32</v>
-      </c>
-      <c r="H52">
-        <v>0.31</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A53">
         <v>52</v>
       </c>
@@ -1764,14 +1434,8 @@
       <c r="F53">
         <v>0.31</v>
       </c>
-      <c r="G53">
-        <v>0.32</v>
-      </c>
-      <c r="H53">
-        <v>0.31</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A54">
         <v>53</v>
       </c>
@@ -1790,14 +1454,8 @@
       <c r="F54">
         <v>0.31</v>
       </c>
-      <c r="G54">
-        <v>0.32</v>
-      </c>
-      <c r="H54">
-        <v>0.31</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A55">
         <v>54</v>
       </c>
@@ -1816,14 +1474,8 @@
       <c r="F55">
         <v>3.11</v>
       </c>
-      <c r="G55">
-        <v>2.16</v>
-      </c>
-      <c r="H55">
-        <v>5.01</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A56">
         <v>55</v>
       </c>
@@ -1842,14 +1494,8 @@
       <c r="F56">
         <v>0.31</v>
       </c>
-      <c r="G56">
-        <v>0.36</v>
-      </c>
-      <c r="H56">
-        <v>0.36</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A57">
         <v>56</v>
       </c>
@@ -1868,14 +1514,8 @@
       <c r="F57">
         <v>0.31</v>
       </c>
-      <c r="G57">
-        <v>0.32</v>
-      </c>
-      <c r="H57">
-        <v>0.32</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A58">
         <v>57</v>
       </c>
@@ -1894,14 +1534,8 @@
       <c r="F58">
         <v>0.31</v>
       </c>
-      <c r="G58">
-        <v>0.32</v>
-      </c>
-      <c r="H58">
-        <v>0.32</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A59">
         <v>58</v>
       </c>
@@ -1920,14 +1554,8 @@
       <c r="F59">
         <v>0.31</v>
       </c>
-      <c r="G59">
-        <v>0.32</v>
-      </c>
-      <c r="H59">
-        <v>0.32</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A60">
         <v>59</v>
       </c>
@@ -1946,14 +1574,8 @@
       <c r="F60">
         <v>2.17</v>
       </c>
-      <c r="G60">
-        <v>2.1800000000000002</v>
-      </c>
-      <c r="H60">
-        <v>3.03</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A61">
         <v>60</v>
       </c>
@@ -1972,14 +1594,8 @@
       <c r="F61">
         <v>19.04</v>
       </c>
-      <c r="G61">
-        <v>84.53</v>
-      </c>
-      <c r="H61">
-        <v>21.5</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A62">
         <v>61</v>
       </c>
@@ -1998,14 +1614,8 @@
       <c r="F62">
         <v>0.31</v>
       </c>
-      <c r="G62">
-        <v>0.34</v>
-      </c>
-      <c r="H62">
-        <v>0.36</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A63">
         <v>62</v>
       </c>
@@ -2024,14 +1634,8 @@
       <c r="F63">
         <v>0.31</v>
       </c>
-      <c r="G63">
-        <v>0.32</v>
-      </c>
-      <c r="H63">
-        <v>0.31</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A64">
         <v>63</v>
       </c>
@@ -2050,14 +1654,8 @@
       <c r="F64">
         <v>306.56</v>
       </c>
-      <c r="G64">
-        <v>301.44</v>
-      </c>
-      <c r="H64">
-        <v>302.87</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A65">
         <v>64</v>
       </c>
@@ -2076,14 +1674,8 @@
       <c r="F65">
         <v>0.31</v>
       </c>
-      <c r="G65">
-        <v>0.32</v>
-      </c>
-      <c r="H65">
-        <v>0.32</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A66">
         <v>65</v>
       </c>
@@ -2102,14 +1694,8 @@
       <c r="F66">
         <v>0.31</v>
       </c>
-      <c r="G66">
-        <v>0.32</v>
-      </c>
-      <c r="H66">
-        <v>0.31</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A67">
         <v>66</v>
       </c>
@@ -2128,14 +1714,8 @@
       <c r="F67">
         <v>17.89</v>
       </c>
-      <c r="G67">
-        <v>300.79000000000002</v>
-      </c>
-      <c r="H67">
-        <v>303.77999999999997</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A68">
         <v>67</v>
       </c>
@@ -2154,14 +1734,8 @@
       <c r="F68">
         <v>2.12</v>
       </c>
-      <c r="G68">
-        <v>2.1800000000000002</v>
-      </c>
-      <c r="H68">
-        <v>4.01</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A69">
         <v>68</v>
       </c>
@@ -2180,14 +1754,8 @@
       <c r="F69">
         <v>3.14</v>
       </c>
-      <c r="G69">
-        <v>5.0599999999999996</v>
-      </c>
-      <c r="H69">
-        <v>8.0399999999999991</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A70">
         <v>69</v>
       </c>
@@ -2206,14 +1774,8 @@
       <c r="F70">
         <v>0.31</v>
       </c>
-      <c r="G70">
-        <v>0.37</v>
-      </c>
-      <c r="H70">
-        <v>0.36</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A71">
         <v>70</v>
       </c>
@@ -2232,14 +1794,8 @@
       <c r="F71">
         <v>0.31</v>
       </c>
-      <c r="G71">
-        <v>0.32</v>
-      </c>
-      <c r="H71">
-        <v>0.31</v>
-      </c>
-    </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A72">
         <v>71</v>
       </c>
@@ -2258,14 +1814,8 @@
       <c r="F72">
         <v>0.31</v>
       </c>
-      <c r="G72">
-        <v>0.32</v>
-      </c>
-      <c r="H72">
-        <v>0.31</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A73">
         <v>72</v>
       </c>
@@ -2284,14 +1834,8 @@
       <c r="F73">
         <v>0.31</v>
       </c>
-      <c r="G73">
-        <v>0.32</v>
-      </c>
-      <c r="H73">
-        <v>0.31</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A74">
         <v>73</v>
       </c>
@@ -2310,14 +1854,8 @@
       <c r="F74">
         <v>0.31</v>
       </c>
-      <c r="G74">
-        <v>0.32</v>
-      </c>
-      <c r="H74">
-        <v>0.31</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A75">
         <v>74</v>
       </c>
@@ -2336,14 +1874,8 @@
       <c r="F75">
         <v>0.31</v>
       </c>
-      <c r="G75">
-        <v>0.32</v>
-      </c>
-      <c r="H75">
-        <v>0.31</v>
-      </c>
-    </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A76">
         <v>75</v>
       </c>
@@ -2362,14 +1894,8 @@
       <c r="F76">
         <v>0.31</v>
       </c>
-      <c r="G76">
-        <v>0.32</v>
-      </c>
-      <c r="H76">
-        <v>0.31</v>
-      </c>
-    </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A77">
         <v>76</v>
       </c>
@@ -2388,14 +1914,8 @@
       <c r="F77">
         <v>0.31</v>
       </c>
-      <c r="G77">
-        <v>0.32</v>
-      </c>
-      <c r="H77">
-        <v>0.31</v>
-      </c>
-    </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A78">
         <v>77</v>
       </c>
@@ -2414,14 +1934,8 @@
       <c r="F78">
         <v>0.31</v>
       </c>
-      <c r="G78">
-        <v>0.32</v>
-      </c>
-      <c r="H78">
-        <v>0.31</v>
-      </c>
-    </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A79">
         <v>78</v>
       </c>
@@ -2440,14 +1954,8 @@
       <c r="F79">
         <v>4.0999999999999996</v>
       </c>
-      <c r="G79">
-        <v>2.1800000000000002</v>
-      </c>
-      <c r="H79">
-        <v>3.03</v>
-      </c>
-    </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A80">
         <v>79</v>
       </c>
@@ -2466,14 +1974,8 @@
       <c r="F80">
         <v>4.0599999999999996</v>
       </c>
-      <c r="G80">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="H80">
-        <v>3.16</v>
-      </c>
-    </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A81">
         <v>80</v>
       </c>
@@ -2492,14 +1994,8 @@
       <c r="F81">
         <v>0.31</v>
       </c>
-      <c r="G81">
-        <v>0.37</v>
-      </c>
-      <c r="H81">
-        <v>0.37</v>
-      </c>
-    </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A82">
         <v>81</v>
       </c>
@@ -2518,14 +2014,8 @@
       <c r="F82">
         <v>0.31</v>
       </c>
-      <c r="G82">
-        <v>0.32</v>
-      </c>
-      <c r="H82">
-        <v>0.31</v>
-      </c>
-    </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A83">
         <v>82</v>
       </c>
@@ -2544,14 +2034,8 @@
       <c r="F83">
         <v>0.31</v>
       </c>
-      <c r="G83">
-        <v>0.32</v>
-      </c>
-      <c r="H83">
-        <v>0.31</v>
-      </c>
-    </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A84">
         <v>83</v>
       </c>
@@ -2570,14 +2054,8 @@
       <c r="F84">
         <v>0.31</v>
       </c>
-      <c r="G84">
-        <v>0.32</v>
-      </c>
-      <c r="H84">
-        <v>0.31</v>
-      </c>
-    </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A85">
         <v>84</v>
       </c>
@@ -2596,14 +2074,8 @@
       <c r="F85">
         <v>0.31</v>
       </c>
-      <c r="G85">
-        <v>0.32</v>
-      </c>
-      <c r="H85">
-        <v>0.31</v>
-      </c>
-    </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A86">
         <v>85</v>
       </c>
@@ -2622,14 +2094,8 @@
       <c r="F86">
         <v>4.0599999999999996</v>
       </c>
-      <c r="G86">
-        <v>3.11</v>
-      </c>
-      <c r="H86">
-        <v>4.05</v>
-      </c>
-    </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A87">
         <v>86</v>
       </c>
@@ -2648,14 +2114,8 @@
       <c r="F87">
         <v>0.31</v>
       </c>
-      <c r="G87">
-        <v>0.37</v>
-      </c>
-      <c r="H87">
-        <v>0.34</v>
-      </c>
-    </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A88">
         <v>87</v>
       </c>
@@ -2674,14 +2134,8 @@
       <c r="F88">
         <v>0.31</v>
       </c>
-      <c r="G88">
-        <v>0.32</v>
-      </c>
-      <c r="H88">
-        <v>0.31</v>
-      </c>
-    </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A89">
         <v>88</v>
       </c>
@@ -2700,14 +2154,8 @@
       <c r="F89">
         <v>0.31</v>
       </c>
-      <c r="G89">
-        <v>0.32</v>
-      </c>
-      <c r="H89">
-        <v>0.31</v>
-      </c>
-    </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A90">
         <v>89</v>
       </c>
@@ -2726,14 +2174,8 @@
       <c r="F90">
         <v>0.31</v>
       </c>
-      <c r="G90">
-        <v>0.32</v>
-      </c>
-      <c r="H90">
-        <v>0.31</v>
-      </c>
-    </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A91">
         <v>90</v>
       </c>
@@ -2752,14 +2194,8 @@
       <c r="F91">
         <v>3.1</v>
       </c>
-      <c r="G91">
-        <v>3.15</v>
-      </c>
-      <c r="H91">
-        <v>5.14</v>
-      </c>
-    </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A92">
         <v>91</v>
       </c>
@@ -2778,14 +2214,8 @@
       <c r="F92">
         <v>0.31</v>
       </c>
-      <c r="G92">
-        <v>0.35</v>
-      </c>
-      <c r="H92">
-        <v>0.36</v>
-      </c>
-    </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A93">
         <v>92</v>
       </c>
@@ -2804,14 +2234,8 @@
       <c r="F93">
         <v>0.31</v>
       </c>
-      <c r="G93">
-        <v>0.32</v>
-      </c>
-      <c r="H93">
-        <v>0.31</v>
-      </c>
-    </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A94">
         <v>93</v>
       </c>
@@ -2830,14 +2254,8 @@
       <c r="F94">
         <v>302.82</v>
       </c>
-      <c r="G94">
-        <v>303.89</v>
-      </c>
-      <c r="H94">
-        <v>302.37</v>
-      </c>
-    </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A95">
         <v>94</v>
       </c>
@@ -2856,14 +2274,8 @@
       <c r="F95">
         <v>7.12</v>
       </c>
-      <c r="G95">
-        <v>5.0199999999999996</v>
-      </c>
-      <c r="H95">
-        <v>6.02</v>
-      </c>
-    </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A96">
         <v>95</v>
       </c>
@@ -2882,14 +2294,8 @@
       <c r="F96">
         <v>0.31</v>
       </c>
-      <c r="G96">
-        <v>0.36</v>
-      </c>
-      <c r="H96">
-        <v>0.36</v>
-      </c>
-    </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A97">
         <v>96</v>
       </c>
@@ -2908,14 +2314,8 @@
       <c r="F97">
         <v>14.77</v>
       </c>
-      <c r="G97">
-        <v>9.92</v>
-      </c>
-      <c r="H97">
-        <v>14.12</v>
-      </c>
-    </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A98">
         <v>97</v>
       </c>
@@ -2934,14 +2334,8 @@
       <c r="F98">
         <v>0.31</v>
       </c>
-      <c r="G98">
-        <v>0.35</v>
-      </c>
-      <c r="H98">
-        <v>0.35</v>
-      </c>
-    </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A99">
         <v>98</v>
       </c>
@@ -2960,14 +2354,8 @@
       <c r="F99">
         <v>0.31</v>
       </c>
-      <c r="G99">
-        <v>0.32</v>
-      </c>
-      <c r="H99">
-        <v>0.31</v>
-      </c>
-    </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A100">
         <v>99</v>
       </c>
@@ -2986,14 +2374,8 @@
       <c r="F100">
         <v>0.31</v>
       </c>
-      <c r="G100">
-        <v>0.32</v>
-      </c>
-      <c r="H100">
-        <v>0.31</v>
-      </c>
-    </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A101">
         <v>100</v>
       </c>
@@ -3010,12 +2392,6 @@
         <v>0.31</v>
       </c>
       <c r="F101">
-        <v>0.31</v>
-      </c>
-      <c r="G101">
-        <v>0.32</v>
-      </c>
-      <c r="H101">
         <v>0.31</v>
       </c>
     </row>
